--- a/04_DESIGN_TABLES/DesignTable_1503.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1503.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2751,24 +2756,56 @@
           <t>1503-04-02-FG</t>
         </is>
       </c>
+      <c r="B38" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.405</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>1503-04-02-FG</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1/4-18 (A NPTF) x 1/8-27 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1503-04-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1503-04-02 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1503-04-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1503-04-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -2779,6 +2816,11 @@
       <c r="Q38" t="inlineStr">
         <is>
           <t>1503-04-02-FG</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2788,24 +2830,56 @@
           <t>1503-04-06-FG</t>
         </is>
       </c>
+      <c r="B39" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.675</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>1503-04-06-FG</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1/4-18 (A NPTF) x 3/8-18 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1503-04-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1503-04-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1503-04-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1503-04-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -2816,6 +2890,11 @@
       <c r="Q39" t="inlineStr">
         <is>
           <t>1503-04-06-FG</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2825,24 +2904,56 @@
           <t>1503-06-04-FG</t>
         </is>
       </c>
+      <c r="B40" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.54</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>1503-06-04-FG</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 1/4-18 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1503-06-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1503-06-04 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1503-06-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1503-06-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -2853,6 +2964,11 @@
       <c r="Q40" t="inlineStr">
         <is>
           <t>1503-06-04-FG</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2862,24 +2978,56 @@
           <t>1503-06-08-FG</t>
         </is>
       </c>
+      <c r="B41" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.84</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>1503-06-08-FG</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 1/2-14 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1503-06-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1503-06-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1503-06-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1503-06-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -2890,6 +3038,11 @@
       <c r="Q41" t="inlineStr">
         <is>
           <t>1503-06-08-FG</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2899,24 +3052,56 @@
           <t>1503-08-12-FG</t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.05</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>1503-08-12-FG</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1/2-14 (A NPTF) x 3/4-14 (A1 NPSM)</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1503-08-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1503-08-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1503-08-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1503-08-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -2927,6 +3112,11 @@
       <c r="Q42" t="inlineStr">
         <is>
           <t>1503-08-12-FG</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
